--- a/Result/profitability/6171.xlsx
+++ b/Result/profitability/6171.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.1</v>
       </c>
       <c r="M2" t="n">
-        <v>1.225</v>
+        <v>0.9474999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>41.8775</v>
+        <v>42.81625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.03</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9162499999999999</v>
+        <v>0.53875</v>
       </c>
       <c r="N3" t="n">
-        <v>37.38874999999999</v>
+        <v>38.39874999999999</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.05</v>
       </c>
       <c r="M4" t="n">
-        <v>0.51</v>
+        <v>0.5412499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>33.28499999999999</v>
+        <v>32.71124999999999</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.02</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5087499999999999</v>
+        <v>0.19625</v>
       </c>
       <c r="N5" t="n">
-        <v>27.53749999999999</v>
+        <v>28.18249999999999</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.05</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1675</v>
+        <v>0.07500000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>23.00749999999999</v>
+        <v>23.43874999999999</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.02</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03750000000000001</v>
+        <v>0.07375000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>18.45624999999999</v>
+        <v>19.50249999999999</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.02</v>
       </c>
       <c r="M8" t="n">
-        <v>0.04125</v>
+        <v>0.06625</v>
       </c>
       <c r="N8" t="n">
-        <v>14.01874999999999</v>
+        <v>14.28124999999999</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6171</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>103</v>
+      </c>
+      <c r="D75" t="n">
+        <v>50</v>
+      </c>
+      <c r="E75" t="n">
+        <v>53</v>
+      </c>
+      <c r="F75" t="n">
+        <v>51.33</v>
+      </c>
+      <c r="G75" t="n">
+        <v>43</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>41.50%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>44</v>
+      </c>
+      <c r="K75" t="n">
+        <v>28</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.2475</v>
+      </c>
+      <c r="N75" t="n">
+        <v>47.56999999999999</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X75" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.100000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.04265691651432046</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.8992805755395683</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>5.159999999999997</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1117608836907082</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
